--- a/simple_game_test/user_rounds_pivot.xlsx
+++ b/simple_game_test/user_rounds_pivot.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1632,85 +1632,434 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
-      <c r="C74" t="n">
-        <v>7</v>
-      </c>
-      <c r="D74" t="n">
-        <v>8</v>
-      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="n">
-        <v>7</v>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>261</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="n">
-        <v>7</v>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>262</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="n">
-        <v>8</v>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>263</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="n">
+        <v>9</v>
+      </c>
+      <c r="E81" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>12</v>
+      </c>
+      <c r="E87" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+      <c r="D88" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="n">
+        <v>12</v>
+      </c>
+      <c r="E89" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" t="n">
         <v>8</v>
       </c>
-      <c r="D78" t="n">
-        <v>9</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="E90" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+      <c r="E92" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>12</v>
+      </c>
+      <c r="E93" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>11</v>
+      </c>
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>7</v>
+      </c>
+      <c r="D97" t="n">
+        <v>8</v>
+      </c>
+      <c r="E97" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>8</v>
+      </c>
+      <c r="E98" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>9</v>
+      </c>
+      <c r="E100" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="n">
+        <v>9</v>
+      </c>
+      <c r="E101" t="n">
         <v>17</v>
       </c>
     </row>
